--- a/projeto/centros_de_custo.xlsx
+++ b/projeto/centros_de_custo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bened\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5155C594-00DE-4C4A-BB5B-5E7FCBDAFC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5470B6B-9D8A-48FA-8D9B-973E8ED51735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{1458C256-756D-4BF1-B610-992632ACD84E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="266">
   <si>
     <t>d7f01dc1-d4cf-4158-ae39-003526a50440</t>
   </si>
@@ -828,6 +828,12 @@
   </si>
   <si>
     <t>69a29be3-2e93-4351-a52d-127972c76430</t>
+  </si>
+  <si>
+    <t>SYMPLA</t>
+  </si>
+  <si>
+    <t>6a38d3d3-6245-4cc2-a9ac-f3a472c232df</t>
   </si>
 </sst>
 </file>
@@ -1207,7 +1213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163D22BB-575F-489C-9799-F85DA17AF1ED}">
-  <dimension ref="A1:C132"/>
+  <dimension ref="A1:C133"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="45.921875" bestFit="1" customWidth="1"/>
@@ -2666,6 +2672,17 @@
         <v>263</v>
       </c>
     </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A133">
+        <v>494</v>
+      </c>
+      <c r="B133" t="s">
+        <v>264</v>
+      </c>
+      <c r="C133" t="s">
+        <v>265</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
